--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Бердянск 130133082.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Бердянск 130133082.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EDCC2D-B5CE-4285-9055-5C3476659F7B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2E2FDC-42C5-44D2-9177-AC65E5544D22}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -164,9 +164,6 @@
     <t>Донецк г, Чаадаева ул. д.1</t>
   </si>
   <si>
-    <t>Мариуполь</t>
-  </si>
-  <si>
     <t>Запорожская область, с. Трояны</t>
   </si>
   <si>
@@ -174,6 +171,9 @@
   </si>
   <si>
     <t>СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>ООО "НОВОЕ ВРЕМЯ" Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -789,47 +789,7 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1265,7 +1225,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1538"/>
+  <dimension ref="A1:N1538"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -1282,7 +1242,7 @@
     <col min="13" max="13" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="27" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1270,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K2" s="26">
         <v>130133082</v>
       </c>
@@ -1324,7 +1284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="31"/>
       <c r="C3" s="7" t="s">
         <v>1</v>
@@ -1340,7 +1300,7 @@
         <v>46212</v>
       </c>
       <c r="G3" s="65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H3" s="63"/>
       <c r="I3" s="63"/>
@@ -1358,7 +1318,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="K4" s="26">
         <v>130133080</v>
       </c>
@@ -1372,7 +1332,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1383,19 +1343,13 @@
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
       <c r="K5" s="26">
-        <v>130439105</v>
+        <v>130439503</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
-      <c r="M5" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="37" t="s">
         <v>4</v>
       </c>
@@ -1405,7 +1359,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
     </row>
-    <row r="7" spans="1:15" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="19.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32" t="s">
         <v>5</v>
       </c>
@@ -1421,8 +1375,8 @@
       <c r="I7" s="24"/>
       <c r="J7" s="24"/>
     </row>
-    <row r="8" spans="1:15" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:15" s="13" customFormat="1" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:14" s="13" customFormat="1" ht="47.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="45" t="s">
         <v>8</v>
       </c>
@@ -1455,7 +1409,7 @@
       </c>
       <c r="K9" s="27"/>
     </row>
-    <row r="10" spans="1:15" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="46"/>
       <c r="B10" s="41" t="s">
         <v>18</v>
@@ -1469,7 +1423,7 @@
       <c r="I10" s="41"/>
       <c r="J10" s="42"/>
     </row>
-    <row r="11" spans="1:15" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="46" t="s">
         <v>22</v>
       </c>
@@ -1485,7 +1439,7 @@
       <c r="I11" s="41"/>
       <c r="J11" s="42"/>
     </row>
-    <row r="12" spans="1:15" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56">
         <v>5897</v>
       </c>
@@ -1514,7 +1468,7 @@
       </c>
       <c r="J12" s="28"/>
     </row>
-    <row r="13" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56">
         <v>6149</v>
       </c>
@@ -1543,7 +1497,7 @@
       </c>
       <c r="J13" s="28"/>
     </row>
-    <row r="14" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56">
         <v>6819</v>
       </c>
@@ -1572,7 +1526,7 @@
       </c>
       <c r="J14" s="28"/>
     </row>
-    <row r="15" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56">
         <v>6202</v>
       </c>
@@ -1601,7 +1555,7 @@
       </c>
       <c r="J15" s="28"/>
     </row>
-    <row r="16" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56">
         <v>6148</v>
       </c>
@@ -1778,7 +1732,7 @@
     <row r="22" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="52"/>
       <c r="B22" s="66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="66"/>
       <c r="D22" s="66"/>
@@ -1794,7 +1748,7 @@
         <v>7216</v>
       </c>
       <c r="B23" s="53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="47" t="s">
         <v>19</v>

--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Бердянск 130133082.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Бердянск 130133082.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2E2FDC-42C5-44D2-9177-AC65E5544D22}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900E1882-22CA-4D04-BE22-C95F56484E49}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -175,6 +175,27 @@
   <si>
     <t>ООО "НОВОЕ ВРЕМЯ" Мариуполь</t>
   </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм кор.0.5кг зам_NEW</t>
+  </si>
+  <si>
+    <t>С КАРТОФ.И ГРИБ.вареники пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>ОСТАНКИНСКИЕ пельм пл. 0.7кг 10шт.зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.42кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм пл.0.7кг зам.</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ ПРЕМИУМ пельм кор.0.4кг зам.</t>
+  </si>
+  <si>
+    <t>СОЧНЫЕ Папа Может пельм 4кг зам.</t>
+  </si>
 </sst>
 </file>
 
@@ -308,7 +329,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,20 +377,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="lightHorizontal">
-        <fgColor indexed="42"/>
-        <bgColor theme="0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -559,30 +568,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="57"/>
-      </left>
-      <right style="double">
-        <color indexed="57"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -592,7 +577,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -744,19 +729,7 @@
     <xf numFmtId="1" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -764,12 +737,6 @@
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -789,48 +756,7 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1249,14 +1175,14 @@
       <c r="D1" s="39">
         <v>130133082</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="64"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="58"/>
       <c r="K1" s="26">
         <v>130133079</v>
       </c>
@@ -1299,12 +1225,12 @@
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="64"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
       <c r="K3" s="26">
         <v>130133081</v>
       </c>
@@ -1440,7 +1366,8 @@
       <c r="J11" s="42"/>
     </row>
     <row r="12" spans="1:14" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="56">
+      <c r="A12" s="53" t="str">
+        <f>RIGHT(D12,4)</f>
         <v>5897</v>
       </c>
       <c r="B12" s="49" t="s">
@@ -1469,7 +1396,8 @@
       <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="56">
+      <c r="A13" s="53" t="str">
+        <f t="shared" ref="A13:A30" si="0">RIGHT(D13,4)</f>
         <v>6149</v>
       </c>
       <c r="B13" s="49" t="s">
@@ -1486,7 +1414,7 @@
         <v>0.3</v>
       </c>
       <c r="G13" s="22">
-        <f t="shared" ref="G13:G19" si="0">E13*F13</f>
+        <f t="shared" ref="G13:G19" si="1">E13*F13</f>
         <v>0</v>
       </c>
       <c r="H13" s="14">
@@ -1498,7 +1426,8 @@
       <c r="J13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56">
+      <c r="A14" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6819</v>
       </c>
       <c r="B14" s="49" t="s">
@@ -1515,7 +1444,7 @@
         <v>0.3</v>
       </c>
       <c r="G14" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="14">
@@ -1527,7 +1456,8 @@
       <c r="J14" s="28"/>
     </row>
     <row r="15" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56">
+      <c r="A15" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6202</v>
       </c>
       <c r="B15" s="49" t="s">
@@ -1544,7 +1474,7 @@
         <v>0.3</v>
       </c>
       <c r="G15" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H15" s="14">
@@ -1556,7 +1486,8 @@
       <c r="J15" s="28"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56">
+      <c r="A16" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6148</v>
       </c>
       <c r="B16" s="49" t="s">
@@ -1573,7 +1504,7 @@
         <v>0.3</v>
       </c>
       <c r="G16" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H16" s="14">
@@ -1585,7 +1516,8 @@
       <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56">
+      <c r="A17" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6209</v>
       </c>
       <c r="B17" s="49" t="s">
@@ -1602,7 +1534,7 @@
         <v>0.35</v>
       </c>
       <c r="G17" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H17" s="14">
@@ -1614,7 +1546,8 @@
       <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="56">
+      <c r="A18" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>6168</v>
       </c>
       <c r="B18" s="49" t="s">
@@ -1631,7 +1564,7 @@
         <v>0.35</v>
       </c>
       <c r="G18" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H18" s="14">
@@ -1643,7 +1576,8 @@
       <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="56">
+      <c r="A19" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5579</v>
       </c>
       <c r="B19" s="49" t="s">
@@ -1660,7 +1594,7 @@
         <v>0.42</v>
       </c>
       <c r="G19" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H19" s="14">
@@ -1672,10 +1606,11 @@
       <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57">
+      <c r="A20" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5754</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="54" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="47" t="s">
@@ -1688,7 +1623,7 @@
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="59">
+      <c r="G20" s="55">
         <f>E20</f>
         <v>0</v>
       </c>
@@ -1701,7 +1636,8 @@
       <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="57">
+      <c r="A21" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>5755</v>
       </c>
       <c r="B21" s="49" t="s">
@@ -1717,7 +1653,7 @@
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="59">
+      <c r="G21" s="55">
         <f>E21</f>
         <v>0</v>
       </c>
@@ -1729,136 +1665,249 @@
       </c>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="52"/>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="60">
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="53" t="str">
+        <f t="shared" si="0"/>
         <v>7216</v>
       </c>
-      <c r="B23" s="53" t="s">
+      <c r="B23" s="54" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="48">
         <v>1002116437216</v>
       </c>
-      <c r="E23" s="54"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="59">
+      <c r="G23" s="55">
         <f>E23*F23</f>
         <v>0</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-    </row>
-    <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="50"/>
-      <c r="B24" s="44" t="s">
+      <c r="I23" s="14"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>6824</v>
+      </c>
+      <c r="B24" s="54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="48">
+        <v>1002112606824</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="G24" s="55">
+        <f t="shared" ref="G24:G29" si="2">E24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7049</v>
+      </c>
+      <c r="B25" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="48">
+        <v>1002151787049</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G25" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7085</v>
+      </c>
+      <c r="B26" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="48">
+        <v>1002112607085</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G26" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7212</v>
+      </c>
+      <c r="B27" s="54" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" s="48">
+        <v>1002112857212</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="22">
+        <v>0.42</v>
+      </c>
+      <c r="G27" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7214</v>
+      </c>
+      <c r="B28" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="48">
+        <v>1002112857214</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="G28" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7224</v>
+      </c>
+      <c r="B29" s="54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" s="48">
+        <v>1002116517224</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="22">
+        <v>0.4</v>
+      </c>
+      <c r="G29" s="55">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>7375</v>
+      </c>
+      <c r="B30" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="48">
+        <v>1002112857375</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="22">
+        <v>1</v>
+      </c>
+      <c r="G30" s="55">
+        <f>E30</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="50"/>
+      <c r="B31" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="16">
-        <f>SUM(E10:E23)</f>
+      <c r="C31" s="15"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="16">
+        <f>SUM(E10:E30)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16">
-        <f>SUM(G12:G23)</f>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16">
+        <f>SUM(G10:G30)</f>
         <v>0</v>
       </c>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="35"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="38"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="35"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="38"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="35"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="38"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="20"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="35"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="38"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="35"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="38"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="35"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="38"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="19"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="35"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="38"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B32" s="35"/>
       <c r="C32" s="17"/>
       <c r="D32" s="38"/>
@@ -16935,16 +16984,6 @@
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="B22:J22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="17" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
